--- a/MIAFPE/MIAFPE.xlsx
+++ b/MIAFPE/MIAFPE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.grygosch\Desktop\FAIRAgro\developement\MIAFPE\MIAFPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2838F28-28E0-455B-9384-5CA8ED5CBB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D8EE5A-A1EF-4726-A832-B134DD8340F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Investigation" sheetId="10" r:id="rId1"/>
@@ -813,7 +813,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -847,6 +847,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1076,17 +1082,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1115,7 +1110,20 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Link" xfId="2" builtinId="8"/>
@@ -1851,7 +1859,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="17"/>
@@ -1875,7 +1883,7 @@
       <c r="T5" s="19"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="39"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -1897,7 +1905,7 @@
       <c r="T6" s="19"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="39"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1919,7 +1927,7 @@
       <c r="T7" s="19"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="39"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1941,7 +1949,7 @@
       <c r="T8" s="19"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1963,7 +1971,7 @@
       <c r="T9" s="20"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="39"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -1985,7 +1993,7 @@
       <c r="T10" s="17"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="40"/>
+      <c r="A11" s="50"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -2029,10 +2037,10 @@
       <c r="B1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="38" t="s">
         <v>177</v>
       </c>
       <c r="E1" s="25" t="s">
@@ -2058,10 +2066,10 @@
       <c r="B2" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="39" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="39" t="s">
         <v>176</v>
       </c>
       <c r="E2" s="26" t="s">
@@ -2087,10 +2095,10 @@
       <c r="B3" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="39" t="s">
         <v>123</v>
       </c>
       <c r="E3" s="26" t="s">
@@ -2116,10 +2124,10 @@
       <c r="B4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="39" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="26" t="s">
@@ -2139,12 +2147,12 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="24"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="24"/>
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
@@ -2152,10 +2160,10 @@
       <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="24"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
       <c r="E6" s="24"/>
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
@@ -2163,10 +2171,10 @@
       <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="24"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="45"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
@@ -2174,10 +2182,10 @@
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="24"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
       <c r="E8" s="24"/>
       <c r="F8" s="24"/>
       <c r="G8" s="24"/>
@@ -2185,10 +2193,10 @@
       <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="41"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="24"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
@@ -2196,10 +2204,10 @@
       <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="24"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
@@ -2207,10 +2215,10 @@
       <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="24"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
@@ -2227,7 +2235,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1A93501-44C1-4A95-8E3F-53204ED54327}">
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:20" ht="51" x14ac:dyDescent="0.25">
@@ -2237,7 +2245,7 @@
       <c r="B1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="46" t="s">
         <v>130</v>
       </c>
       <c r="D1" s="25" t="s">
@@ -2255,13 +2263,13 @@
       <c r="H1" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="46" t="s">
+      <c r="I1" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="J1" s="46" t="s">
+      <c r="J1" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="41" t="s">
         <v>138</v>
       </c>
       <c r="L1" s="25" t="s">
@@ -2273,22 +2281,22 @@
       <c r="N1" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="O1" s="50" t="s">
+      <c r="O1" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="P1" s="50" t="s">
+      <c r="P1" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="Q1" s="50" t="s">
+      <c r="Q1" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="R1" s="50" t="s">
+      <c r="R1" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="S1" s="50" t="s">
+      <c r="S1" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="T1" s="50" t="s">
+      <c r="T1" s="45" t="s">
         <v>194</v>
       </c>
     </row>
@@ -2305,7 +2313,7 @@
       <c r="D2" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="42" t="s">
         <v>145</v>
       </c>
       <c r="F2" s="7" t="s">
@@ -2317,19 +2325,19 @@
       <c r="H2" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="42" t="s">
         <v>149</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="42" t="s">
         <v>151</v>
       </c>
       <c r="L2" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="42" t="s">
         <v>153</v>
       </c>
       <c r="N2" s="7" t="s">
@@ -2367,13 +2375,13 @@
       <c r="H3" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I3" s="47" t="s">
+      <c r="I3" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="J3" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="47" t="s">
         <v>163</v>
       </c>
       <c r="L3" s="7" t="s">
@@ -2417,13 +2425,13 @@
       <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="42" t="s">
         <v>168</v>
       </c>
-      <c r="J4" s="47" t="s">
+      <c r="J4" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="42" t="s">
         <v>169</v>
       </c>
       <c r="L4" s="7" t="s">
@@ -2455,7 +2463,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="24"/>
@@ -2465,9 +2473,9 @@
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
       <c r="H5" s="24"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
       <c r="N5" s="24"/>
@@ -2479,7 +2487,7 @@
       <c r="T5" s="24"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -2487,9 +2495,9 @@
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
       <c r="N6" s="24"/>
@@ -2501,7 +2509,7 @@
       <c r="T6" s="24"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -2509,9 +2517,9 @@
       <c r="F7" s="23"/>
       <c r="G7" s="23"/>
       <c r="H7" s="23"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="44"/>
+      <c r="K7" s="44"/>
       <c r="L7" s="23"/>
       <c r="M7" s="23"/>
       <c r="N7" s="23"/>
@@ -2523,7 +2531,7 @@
       <c r="T7" s="23"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -2531,9 +2539,9 @@
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
       <c r="L8" s="23"/>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
@@ -2545,7 +2553,7 @@
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="41"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="30"/>
@@ -2553,9 +2561,9 @@
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="44"/>
+      <c r="K9" s="44"/>
       <c r="L9" s="23"/>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -2567,7 +2575,7 @@
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -2575,9 +2583,9 @@
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
       <c r="N10" s="23"/>
@@ -2589,7 +2597,7 @@
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -2597,9 +2605,9 @@
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
-      <c r="I11" s="49"/>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49"/>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+      <c r="K11" s="44"/>
       <c r="L11" s="23"/>
       <c r="M11" s="23"/>
       <c r="N11" s="23"/>
@@ -2609,10 +2617,6 @@
       <c r="R11" s="23"/>
       <c r="S11" s="23"/>
       <c r="T11" s="23"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2703,7 +2707,7 @@
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="23"/>
@@ -2716,7 +2720,7 @@
       <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -2727,7 +2731,7 @@
       <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -2738,7 +2742,7 @@
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -2749,7 +2753,7 @@
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="41"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -2760,7 +2764,7 @@
       <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -2771,7 +2775,7 @@
       <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -2813,13 +2817,13 @@
       <c r="F1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="53" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="53" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="53" t="s">
         <v>185</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -2883,7 +2887,7 @@
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="23"/>
@@ -2898,7 +2902,7 @@
       <c r="K5" s="24"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -2911,7 +2915,7 @@
       <c r="K6" s="24"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -2924,7 +2928,7 @@
       <c r="K7" s="24"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -2937,7 +2941,7 @@
       <c r="K8" s="23"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="41"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -2950,7 +2954,7 @@
       <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -2963,7 +2967,7 @@
       <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -3057,7 +3061,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="48" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="23"/>
@@ -3066,42 +3070,42 @@
       <c r="E5" s="24"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="41"/>
+      <c r="A6" s="51"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="41"/>
+      <c r="A7" s="51"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
       <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="41"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="41"/>
+      <c r="A9" s="51"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="41"/>
+      <c r="A10" s="51"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>

--- a/MIAFPE/MIAFPE.xlsx
+++ b/MIAFPE/MIAFPE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l.grygosch\Desktop\FAIRAgro\developement\MIAFPE\MIAFPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D8EE5A-A1EF-4726-A832-B134DD8340F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A29E78-71A4-490C-B75F-9314B95027DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{683B011A-2F29-4327-800E-1A9041681AF0}"/>
   </bookViews>
   <sheets>
     <sheet name="Investigation" sheetId="10" r:id="rId1"/>
@@ -813,7 +813,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -853,6 +853,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -971,7 +977,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1110,6 +1116,9 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -1121,8 +1130,19 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1859,7 +1879,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="17"/>
@@ -1883,7 +1903,7 @@
       <c r="T5" s="19"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
+      <c r="A6" s="50"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
       <c r="D6" s="17"/>
@@ -1905,7 +1925,7 @@
       <c r="T6" s="19"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
+      <c r="A7" s="50"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1927,7 +1947,7 @@
       <c r="T7" s="19"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
+      <c r="A8" s="50"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -1949,7 +1969,7 @@
       <c r="T8" s="19"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
+      <c r="A9" s="50"/>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -1971,7 +1991,7 @@
       <c r="T9" s="20"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="49"/>
+      <c r="A10" s="50"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -1993,7 +2013,7 @@
       <c r="T10" s="17"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="50"/>
+      <c r="A11" s="51"/>
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -2147,7 +2167,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="24"/>
@@ -2160,7 +2180,7 @@
       <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="24"/>
       <c r="C6" s="40"/>
       <c r="D6" s="40"/>
@@ -2171,7 +2191,7 @@
       <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="24"/>
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
@@ -2182,7 +2202,7 @@
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="24"/>
       <c r="C8" s="40"/>
       <c r="D8" s="40"/>
@@ -2193,7 +2213,7 @@
       <c r="I8" s="24"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="24"/>
       <c r="C9" s="40"/>
       <c r="D9" s="40"/>
@@ -2204,7 +2224,7 @@
       <c r="I9" s="24"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="24"/>
       <c r="C10" s="40"/>
       <c r="D10" s="40"/>
@@ -2215,7 +2235,7 @@
       <c r="I10" s="24"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="24"/>
       <c r="C11" s="40"/>
       <c r="D11" s="40"/>
@@ -2463,7 +2483,7 @@
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="24"/>
@@ -2487,7 +2507,7 @@
       <c r="T5" s="24"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -2509,7 +2529,7 @@
       <c r="T6" s="24"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
@@ -2531,7 +2551,7 @@
       <c r="T7" s="23"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -2553,7 +2573,7 @@
       <c r="T8" s="23"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="30"/>
@@ -2575,7 +2595,7 @@
       <c r="T9" s="23"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -2597,7 +2617,7 @@
       <c r="T10" s="23"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -2633,6 +2653,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE2ED500-E32B-426B-8C81-BE5153830C8D}">
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="5" width="11.42578125" style="58"/>
+    <col min="9" max="9" width="21.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -2644,10 +2668,10 @@
       <c r="C1" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="54" t="s">
         <v>197</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -2671,8 +2695,8 @@
         <v>186</v>
       </c>
       <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="10"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="59"/>
       <c r="F2" s="10"/>
       <c r="G2" s="7"/>
       <c r="H2" s="10"/>
@@ -2686,8 +2710,8 @@
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="10"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="10"/>
       <c r="G3" s="21"/>
       <c r="H3" s="10"/>
@@ -2699,87 +2723,87 @@
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
       <c r="H5" s="24"/>
       <c r="I5" s="24"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="D6" s="56"/>
+      <c r="E6" s="56"/>
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
       <c r="I6" s="24"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
       <c r="H7" s="24"/>
       <c r="I7" s="24"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="23"/>
       <c r="G8" s="23"/>
       <c r="H8" s="23"/>
       <c r="I8" s="23"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
       <c r="F9" s="23"/>
       <c r="G9" s="23"/>
       <c r="H9" s="23"/>
       <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
       <c r="F10" s="23"/>
       <c r="G10" s="23"/>
       <c r="H10" s="23"/>
       <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
       <c r="F11" s="23"/>
       <c r="G11" s="23"/>
       <c r="H11" s="23"/>
@@ -2817,13 +2841,13 @@
       <c r="F1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="G1" s="53" t="s">
+      <c r="G1" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="48" t="s">
         <v>185</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -2887,7 +2911,7 @@
       <c r="K4" s="7"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="23"/>
@@ -2902,7 +2926,7 @@
       <c r="K5" s="24"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -2915,7 +2939,7 @@
       <c r="K6" s="24"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
@@ -2928,7 +2952,7 @@
       <c r="K7" s="24"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
@@ -2941,7 +2965,7 @@
       <c r="K8" s="23"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
@@ -2954,7 +2978,7 @@
       <c r="K9" s="23"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
@@ -2967,7 +2991,7 @@
       <c r="K10" s="23"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
@@ -3061,7 +3085,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="23"/>
@@ -3070,42 +3094,42 @@
       <c r="E5" s="24"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="23"/>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="23"/>
       <c r="C7" s="24"/>
       <c r="D7" s="24"/>
       <c r="E7" s="24"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="23"/>
       <c r="C8" s="23"/>
       <c r="D8" s="23"/>
       <c r="E8" s="23"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="23"/>
       <c r="C9" s="23"/>
       <c r="D9" s="23"/>
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="23"/>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="23"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="23"/>
       <c r="C11" s="23"/>
       <c r="D11" s="23"/>
